--- a/JP (Exclude Game)/Dialog/Drama/loytel.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/loytel.xlsx
@@ -3694,7 +3694,7 @@
 魔石があの男をどのような恐ろしい化け物に変えたかは、汝らも耳にしているだろう。不浄なる闇、亡者を操る呪われた死霊使い…ひとたびその名が囁かれれば、子どもは泣き、大人ですら震え上がる穢れた存在だ。</t>
   </si>
   <si>
-    <t xml:space="preserve">Soon after, a figure cloaked in black bagan to visit Kettle, time and again, as though the bond between master and student had never been severed.
+    <t xml:space="preserve">Soon after, a figure cloaked in black began to visit Kettle, time and again, as though the bond between master and student had never been severed.
 A man in black... heh heh heh... indeed, Issizzle still remained human then.
 But thou knowest well what dread monster the Magic Stone eventually made of him. An unholy darkness, a necromancer who commands the dead... whose whispered name strikes terror into children and adults alike.</t>
   </si>
@@ -3760,7 +3760,7 @@
     <t xml:space="preserve">ミシリアの東の山脈のふもと、暗く古い森の中に、我々「追放者」の暮らす村がある。結界に守られているが、この腕輪があれば拒まれることはない。</t>
   </si>
   <si>
-    <t xml:space="preserve">In the shadow of the eastern mountains of Mysiria lies a dark, ancient forest. There, thou wilt find the village of the Exiles—my kin, my kindred. It is shielded by a barrier, yet this bracelet shall grant thee passage.
+    <t xml:space="preserve">In the shadow of the eastern mountains of Mysilia lies a dark, ancient forest. There, thou wilt find the village of the Exiles—my kin, my kindred. It is shielded by a barrier, yet this bracelet shall grant thee passage.
 </t>
   </si>
   <si>
